--- a/docs/experiments/benchmark_all_systems.xlsx
+++ b/docs/experiments/benchmark_all_systems.xlsx
@@ -587,7 +587,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:W20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A perfect marker marks every answer (the upper limit)</t>
+          <t>The answer key used as the marker (the upper limit)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verdict-only pass with the exact-match oracle</t>
+          <t>Verdict-only pass with the exact-match oracle; no second model is loaded</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -2207,7 +2207,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>

--- a/docs/experiments/benchmark_all_systems.xlsx
+++ b/docs/experiments/benchmark_all_systems.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Benchmark" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Column guide" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column guide" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
